--- a/testExcel/User Story Document.xlsx
+++ b/testExcel/User Story Document.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -456,447 +456,357 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>User Story Document</t>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Project Name: Online Shopping Application</t>
+          <t>| Verify Valid EDI 270 Inquiry File Generation for Delinquency Status | TC-EDI270-271-DEL-001 | sample_edi270_valid_01.txt | Draft |</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Prepared By: Product Team</t>
+          <t>| Positive | Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Date: 08-Jan-2026</t>
+          <t>file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Version: 1.0</t>
+          <t>elements comply with the specification.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1. User Story Overview</t>
+          <t>| System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available. | 1 | Prepare valid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Field	Details</t>
+          <t>subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID. | Input data is prepared with correct formats and</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>User Story ID	US-001</t>
+          <t>trading partner identifiers.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Title	User Login to Application</t>
+          <t>| sample_input_270.json |</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Epic	User Authentication</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Priority	High</t>
+          <t>| | | | |</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sprint	Sprint 1</t>
+          <t>| 2 | Generate the 270 file using the</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Status	New</t>
+          <t>prepared input data. | The 270 file is generated with correct ISA/GS headers, ST/BHT segments,</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2. User Story Statement</t>
+          <t>and subscriber loops populated. The file contains no syntax errors.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>As a registered user</t>
+          <t>| generated_270_01.txt |</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>I want to log in to the application using my email and password</t>
+          <t>| |</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>So that I can access my personal account and place orders</t>
+          <t>| 3 | Validate the generated 270 file</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>3. Description</t>
+          <t>against the ANSI X12 270 schema and implementation guide. | The 270 file passes schema validation with no missing mandatory</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The user should be able to log in using valid credentials.</t>
+          <t>segments or invalid data elements.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>If the credentials are correct, the system should redirect the user to the dashboard.</t>
+          <t>| 270_schema_validation_report.json |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>If incorrect, an error message should be displayed.</t>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>4. Acceptance Criteria</t>
+          <t>| Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation) | TC-EDI270-271-DEL-002 | sample_edi271_valid_01.txt |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>No.	Acceptance Criteria</t>
+          <t>| Draft | Positive | Validate that the 271 response file generated for a member with delinquency status "Active - Pending Investigation" includes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>1	User must be able to enter email and password</t>
+          <t>the EB segment in loop 2110C with EB01 set to "5" as per the business rule when the SBWM_EFF_DT is within 0-30 days. Confirm all other EB segment elements</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2	System validates email and password</t>
+          <t>remain unchanged and the file passes schema validation.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>3	User is redirected to dashboard on successful login</t>
+          <t>| Valid 270 inquiry submitted for member with delinquency status active within 0-30 days. | 1 | Receive the 271 response file</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>4	Error message shown for invalid credentials</t>
+          <t>corresponding to the 270 inquiry. | 271 file is received containing loop 2110C with EB segment having</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>5	Login button disabled if fields are empty</t>
+          <t>EB01 = "5".</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>5. Business Rules</t>
+          <t>| generated_271_01.txt |</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Email must be registered</t>
+          <t>|</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Password must be encrypted</t>
+          <t>| | | |</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Maximum 5 failed attempts allowed</t>
+          <t>| 2 | Validate the 271 file against the</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Account locked after 5 failures</t>
+          <t>ANSI X12 271 schema and implementation guide. | 271 file passes schema validation with required segments including ISA,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>6. Assumptions</t>
+          <t>GS, ST, BHT, HL, NM1, REF, DTP, and EB segments correctly populated.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>User is already registered</t>
+          <t>| 271_schema_validation_report.json |</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Internet connection is available</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Backend authentication service is active</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>7. Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>User Registration Module</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Authentication API</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Database connectivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>8. UI/UX Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Login page should be responsive</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Show password toggle (eye icon)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Display error messages in red</t>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>

--- a/testExcel/User Story Document.xlsx
+++ b/testExcel/User Story Document.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
+          <t>[</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>| Verify Valid EDI 270 Inquiry File Generation for Delinquency Status | TC-EDI270-271-DEL-001 | sample_edi270_valid_01.txt | Draft |</t>
+          <t>{</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>| Positive | Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the</t>
+          <t>"user_story_id": "US-001",</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data</t>
+          <t>"title": "Generate EDI 270 Inquiry File",</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>elements comply with the specification.</t>
+          <t>"description": "As a user, I want to generate a valid EDI 270 inquiry file so that eligibility requests can be processed successfully.",</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>| System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available. | 1 | Prepare valid</t>
+          <t>"priority": "High",</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID. | Input data is prepared with correct formats and</t>
+          <t>"status": "Draft"</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>trading partner identifiers.</t>
+          <t>},</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>| sample_input_270.json |</t>
+          <t>{</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>"user_story_id": "US-002",</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>| | | | |</t>
+          <t>"title": "Validate EDI 271 Response",</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>| 2 | Generate the 270 file using the</t>
+          <t>"description": "As a user, I want to validate the EDI 271 response file so that delinquency status details are correctly received.",</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>prepared input data. | The 270 file is generated with correct ISA/GS headers, ST/BHT segments,</t>
+          <t>"priority": "Medium",</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>and subscriber loops populated. The file contains no syntax errors.</t>
+          <t>"status": "Draft"</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>| generated_270_01.txt |</t>
+          <t>}</t>
         </is>
       </c>
     </row>
@@ -606,207 +606,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>| |</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>| 3 | Validate the generated 270 file</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>against the ANSI X12 270 schema and implementation guide. | The 270 file passes schema validation with no missing mandatory</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>segments or invalid data elements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>| 270_schema_validation_report.json |</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>| Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation) | TC-EDI270-271-DEL-002 | sample_edi271_valid_01.txt |</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>| Draft | Positive | Validate that the 271 response file generated for a member with delinquency status "Active - Pending Investigation" includes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>the EB segment in loop 2110C with EB01 set to "5" as per the business rule when the SBWM_EFF_DT is within 0-30 days. Confirm all other EB segment elements</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>remain unchanged and the file passes schema validation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>| Valid 270 inquiry submitted for member with delinquency status active within 0-30 days. | 1 | Receive the 271 response file</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>corresponding to the 270 inquiry. | 271 file is received containing loop 2110C with EB segment having</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>EB01 = "5".</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>| generated_271_01.txt |</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>| | | |</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>| 2 | Validate the 271 file against the</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>ANSI X12 271 schema and implementation guide. | 271 file passes schema validation with required segments including ISA,</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>GS, ST, BHT, HL, NM1, REF, DTP, and EB segments correctly populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>| 271_schema_validation_report.json |</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
+          <t>]</t>
         </is>
       </c>
     </row>

--- a/testExcel/User Story Document.xlsx
+++ b/testExcel/User Story Document.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>[</t>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>{</t>
+          <t>| Verify Valid EDI 270 Inquiry File Generation for Delinquency Status | TC-EDI270-271-DEL-001 | sample_edi270_valid_01.txt | Draft |</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>"user_story_id": "US-001",</t>
+          <t>| Positive | Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>"title": "Generate EDI 270 Inquiry File",</t>
+          <t>file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>"description": "As a user, I want to generate a valid EDI 270 inquiry file so that eligibility requests can be processed successfully.",</t>
+          <t>elements comply with the specification.</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>"priority": "High",</t>
+          <t>| System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available. | 1 | Prepare valid</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>"status": "Draft"</t>
+          <t>subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID. | Input data is prepared with correct formats and</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>},</t>
+          <t>trading partner identifiers.</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>{</t>
+          <t>| sample_input_270.json |</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>"user_story_id": "US-002",</t>
+          <t>|</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>"title": "Validate EDI 271 Response",</t>
+          <t>| | | | |</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>"description": "As a user, I want to validate the EDI 271 response file so that delinquency status details are correctly received.",</t>
+          <t>| 2 | Generate the 270 file using the</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>"priority": "Medium",</t>
+          <t>prepared input data. | The 270 file is generated with correct ISA/GS headers, ST/BHT segments,</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>"status": "Draft"</t>
+          <t>and subscriber loops populated. The file contains no syntax errors.</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>}</t>
+          <t>| generated_270_01.txt |</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,207 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>]</t>
+          <t>| |</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>| 3 | Validate the generated 270 file</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>against the ANSI X12 270 schema and implementation guide. | The 270 file passes schema validation with no missing mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>segments or invalid data elements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>| 270_schema_validation_report.json |</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>| Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation) | TC-EDI270-271-DEL-002 | sample_edi271_valid_01.txt |</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>| Draft | Positive | Validate that the 271 response file generated for a member with delinquency status "Active - Pending Investigation" includes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>the EB segment in loop 2110C with EB01 set to "5" as per the business rule when the SBWM_EFF_DT is within 0-30 days. Confirm all other EB segment elements</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>remain unchanged and the file passes schema validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>| Valid 270 inquiry submitted for member with delinquency status active within 0-30 days. | 1 | Receive the 271 response file</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>corresponding to the 270 inquiry. | 271 file is received containing loop 2110C with EB segment having</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>EB01 = "5".</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>| generated_271_01.txt |</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>| | | |</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>| 2 | Validate the 271 file against the</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>ANSI X12 271 schema and implementation guide. | 271 file passes schema validation with required segments including ISA,</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>GS, ST, BHT, HL, NM1, REF, DTP, and EB segments correctly populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>| 271_schema_validation_report.json |</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>------------------------------------------------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
